--- a/tests/use_cases/casos_de_uso.xlsx
+++ b/tests/use_cases/casos_de_uso.xlsx
@@ -76,12 +76,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -629,12 +629,12 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Envia credenciais; valida usuário/senha; gera JWT; retorna 200.</t>
+          <t>Servidor OU pesquisador envia credenciais; valida usuário/senha; gera JWT (role = papel do usuário); 200.</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>A1 pesquisador (role no token); A2 validação de aba no front.</t>
+          <t>A1 validação da aba ADM/Pesquisador no frontend (regra de UI).</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -1282,14 +1282,14 @@
           <t>UC01</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>Alternativo</t>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Principal</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Login de pesquisador de campo</t>
+          <t>Login de pesquisador (mesmo fluxo, outro ator)</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -1320,7 +1320,7 @@
           <t>UC01</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -1358,7 +1358,7 @@
           <t>UC01</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -1396,7 +1396,7 @@
           <t>UC01</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -1434,14 +1434,14 @@
           <t>UC01</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>Alternativo</t>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Principal</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Conteúdo do token (claims)</t>
+          <t>Conteúdo do token (claims do fluxo principal)</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1510,7 +1510,7 @@
           <t>UC02</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>Alternativo</t>
         </is>
@@ -1548,7 +1548,7 @@
           <t>UC02</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>Alternativo</t>
         </is>
@@ -1586,7 +1586,7 @@
           <t>UC02</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -1624,7 +1624,7 @@
           <t>UC02</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -1662,7 +1662,7 @@
           <t>UC02</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -1700,7 +1700,7 @@
           <t>UC02</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -1738,7 +1738,7 @@
           <t>UC02</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>Alternativo</t>
         </is>
@@ -1814,7 +1814,7 @@
           <t>UC03</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>Alternativo</t>
         </is>
@@ -1852,7 +1852,7 @@
           <t>UC03</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>Alternativo</t>
         </is>
@@ -1890,7 +1890,7 @@
           <t>UC03</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>Alternativo</t>
         </is>
@@ -1928,7 +1928,7 @@
           <t>UC03</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>Alternativo</t>
         </is>
@@ -1966,7 +1966,7 @@
           <t>UC03</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>Alternativo</t>
         </is>
@@ -2004,7 +2004,7 @@
           <t>UC03</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>Alternativo</t>
         </is>
@@ -2042,7 +2042,7 @@
           <t>UC03</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -2080,7 +2080,7 @@
           <t>UC03</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -2118,7 +2118,7 @@
           <t>UC03</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="C27" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -2156,7 +2156,7 @@
           <t>UC03</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -2232,7 +2232,7 @@
           <t>UC04</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>Alternativo</t>
         </is>
@@ -2270,7 +2270,7 @@
           <t>UC04</t>
         </is>
       </c>
-      <c r="C31" s="10" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>Alternativo</t>
         </is>
@@ -2308,7 +2308,7 @@
           <t>UC04</t>
         </is>
       </c>
-      <c r="C32" s="10" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>Alternativo</t>
         </is>
@@ -2346,7 +2346,7 @@
           <t>UC04</t>
         </is>
       </c>
-      <c r="C33" s="10" t="inlineStr">
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>Alternativo</t>
         </is>
@@ -2384,7 +2384,7 @@
           <t>UC04</t>
         </is>
       </c>
-      <c r="C34" s="10" t="inlineStr">
+      <c r="C34" s="11" t="inlineStr">
         <is>
           <t>Alternativo</t>
         </is>
@@ -2422,7 +2422,7 @@
           <t>UC04</t>
         </is>
       </c>
-      <c r="C35" s="11" t="inlineStr">
+      <c r="C35" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -2460,7 +2460,7 @@
           <t>UC04</t>
         </is>
       </c>
-      <c r="C36" s="11" t="inlineStr">
+      <c r="C36" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -2498,7 +2498,7 @@
           <t>UC04</t>
         </is>
       </c>
-      <c r="C37" s="11" t="inlineStr">
+      <c r="C37" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -2536,7 +2536,7 @@
           <t>UC04</t>
         </is>
       </c>
-      <c r="C38" s="11" t="inlineStr">
+      <c r="C38" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -2612,7 +2612,7 @@
           <t>UC05</t>
         </is>
       </c>
-      <c r="C40" s="10" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>Alternativo</t>
         </is>
@@ -2650,7 +2650,7 @@
           <t>UC05</t>
         </is>
       </c>
-      <c r="C41" s="10" t="inlineStr">
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>Alternativo</t>
         </is>
@@ -2688,7 +2688,7 @@
           <t>UC05</t>
         </is>
       </c>
-      <c r="C42" s="11" t="inlineStr">
+      <c r="C42" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -2726,7 +2726,7 @@
           <t>UC05</t>
         </is>
       </c>
-      <c r="C43" s="11" t="inlineStr">
+      <c r="C43" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -2764,7 +2764,7 @@
           <t>UC05</t>
         </is>
       </c>
-      <c r="C44" s="11" t="inlineStr">
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -2802,7 +2802,7 @@
           <t>UC05</t>
         </is>
       </c>
-      <c r="C45" s="11" t="inlineStr">
+      <c r="C45" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -2840,7 +2840,7 @@
           <t>UC05</t>
         </is>
       </c>
-      <c r="C46" s="11" t="inlineStr">
+      <c r="C46" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -2878,7 +2878,7 @@
           <t>UC05</t>
         </is>
       </c>
-      <c r="C47" s="11" t="inlineStr">
+      <c r="C47" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -2916,7 +2916,7 @@
           <t>UC05</t>
         </is>
       </c>
-      <c r="C48" s="11" t="inlineStr">
+      <c r="C48" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -2992,7 +2992,7 @@
           <t>UC06</t>
         </is>
       </c>
-      <c r="C50" s="10" t="inlineStr">
+      <c r="C50" s="11" t="inlineStr">
         <is>
           <t>Alternativo</t>
         </is>
@@ -3030,7 +3030,7 @@
           <t>UC06</t>
         </is>
       </c>
-      <c r="C51" s="10" t="inlineStr">
+      <c r="C51" s="11" t="inlineStr">
         <is>
           <t>Alternativo</t>
         </is>
@@ -3068,7 +3068,7 @@
           <t>UC06</t>
         </is>
       </c>
-      <c r="C52" s="11" t="inlineStr">
+      <c r="C52" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -3106,7 +3106,7 @@
           <t>UC06</t>
         </is>
       </c>
-      <c r="C53" s="11" t="inlineStr">
+      <c r="C53" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -3144,7 +3144,7 @@
           <t>UC06</t>
         </is>
       </c>
-      <c r="C54" s="11" t="inlineStr">
+      <c r="C54" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -3182,7 +3182,7 @@
           <t>UC06</t>
         </is>
       </c>
-      <c r="C55" s="11" t="inlineStr">
+      <c r="C55" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -3220,7 +3220,7 @@
           <t>UC06</t>
         </is>
       </c>
-      <c r="C56" s="11" t="inlineStr">
+      <c r="C56" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -3258,7 +3258,7 @@
           <t>UC06</t>
         </is>
       </c>
-      <c r="C57" s="11" t="inlineStr">
+      <c r="C57" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -3334,7 +3334,7 @@
           <t>UC07</t>
         </is>
       </c>
-      <c r="C59" s="10" t="inlineStr">
+      <c r="C59" s="11" t="inlineStr">
         <is>
           <t>Alternativo</t>
         </is>
@@ -3372,7 +3372,7 @@
           <t>UC07</t>
         </is>
       </c>
-      <c r="C60" s="10" t="inlineStr">
+      <c r="C60" s="11" t="inlineStr">
         <is>
           <t>Alternativo</t>
         </is>
@@ -3410,7 +3410,7 @@
           <t>UC07</t>
         </is>
       </c>
-      <c r="C61" s="10" t="inlineStr">
+      <c r="C61" s="11" t="inlineStr">
         <is>
           <t>Alternativo</t>
         </is>
@@ -3448,7 +3448,7 @@
           <t>UC07</t>
         </is>
       </c>
-      <c r="C62" s="10" t="inlineStr">
+      <c r="C62" s="11" t="inlineStr">
         <is>
           <t>Alternativo</t>
         </is>
@@ -3486,7 +3486,7 @@
           <t>UC07</t>
         </is>
       </c>
-      <c r="C63" s="10" t="inlineStr">
+      <c r="C63" s="11" t="inlineStr">
         <is>
           <t>Alternativo</t>
         </is>
@@ -3524,7 +3524,7 @@
           <t>UC07</t>
         </is>
       </c>
-      <c r="C64" s="11" t="inlineStr">
+      <c r="C64" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -3562,7 +3562,7 @@
           <t>UC07</t>
         </is>
       </c>
-      <c r="C65" s="11" t="inlineStr">
+      <c r="C65" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -3600,7 +3600,7 @@
           <t>UC07</t>
         </is>
       </c>
-      <c r="C66" s="11" t="inlineStr">
+      <c r="C66" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -3638,7 +3638,7 @@
           <t>UC07</t>
         </is>
       </c>
-      <c r="C67" s="11" t="inlineStr">
+      <c r="C67" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -3714,7 +3714,7 @@
           <t>UC08</t>
         </is>
       </c>
-      <c r="C69" s="10" t="inlineStr">
+      <c r="C69" s="11" t="inlineStr">
         <is>
           <t>Alternativo</t>
         </is>
@@ -3752,7 +3752,7 @@
           <t>UC08</t>
         </is>
       </c>
-      <c r="C70" s="10" t="inlineStr">
+      <c r="C70" s="11" t="inlineStr">
         <is>
           <t>Alternativo</t>
         </is>
@@ -3790,7 +3790,7 @@
           <t>UC08</t>
         </is>
       </c>
-      <c r="C71" s="10" t="inlineStr">
+      <c r="C71" s="11" t="inlineStr">
         <is>
           <t>Alternativo</t>
         </is>
@@ -3828,7 +3828,7 @@
           <t>UC08</t>
         </is>
       </c>
-      <c r="C72" s="10" t="inlineStr">
+      <c r="C72" s="11" t="inlineStr">
         <is>
           <t>Alternativo</t>
         </is>
@@ -3866,7 +3866,7 @@
           <t>UC08</t>
         </is>
       </c>
-      <c r="C73" s="10" t="inlineStr">
+      <c r="C73" s="11" t="inlineStr">
         <is>
           <t>Alternativo</t>
         </is>
@@ -3904,7 +3904,7 @@
           <t>UC08</t>
         </is>
       </c>
-      <c r="C74" s="11" t="inlineStr">
+      <c r="C74" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -3942,7 +3942,7 @@
           <t>UC08</t>
         </is>
       </c>
-      <c r="C75" s="11" t="inlineStr">
+      <c r="C75" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -3980,7 +3980,7 @@
           <t>UC08</t>
         </is>
       </c>
-      <c r="C76" s="11" t="inlineStr">
+      <c r="C76" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -4018,7 +4018,7 @@
           <t>UC08</t>
         </is>
       </c>
-      <c r="C77" s="11" t="inlineStr">
+      <c r="C77" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -4094,7 +4094,7 @@
           <t>UC09</t>
         </is>
       </c>
-      <c r="C79" s="10" t="inlineStr">
+      <c r="C79" s="11" t="inlineStr">
         <is>
           <t>Alternativo</t>
         </is>
@@ -4132,7 +4132,7 @@
           <t>UC09</t>
         </is>
       </c>
-      <c r="C80" s="10" t="inlineStr">
+      <c r="C80" s="11" t="inlineStr">
         <is>
           <t>Alternativo</t>
         </is>
@@ -4170,7 +4170,7 @@
           <t>UC09</t>
         </is>
       </c>
-      <c r="C81" s="10" t="inlineStr">
+      <c r="C81" s="11" t="inlineStr">
         <is>
           <t>Alternativo</t>
         </is>
@@ -4208,7 +4208,7 @@
           <t>UC09</t>
         </is>
       </c>
-      <c r="C82" s="10" t="inlineStr">
+      <c r="C82" s="11" t="inlineStr">
         <is>
           <t>Alternativo</t>
         </is>
@@ -4246,7 +4246,7 @@
           <t>UC09</t>
         </is>
       </c>
-      <c r="C83" s="11" t="inlineStr">
+      <c r="C83" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -4284,7 +4284,7 @@
           <t>UC09</t>
         </is>
       </c>
-      <c r="C84" s="11" t="inlineStr">
+      <c r="C84" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -4322,7 +4322,7 @@
           <t>UC09</t>
         </is>
       </c>
-      <c r="C85" s="11" t="inlineStr">
+      <c r="C85" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -4360,7 +4360,7 @@
           <t>UC09</t>
         </is>
       </c>
-      <c r="C86" s="11" t="inlineStr">
+      <c r="C86" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -4398,7 +4398,7 @@
           <t>UC09</t>
         </is>
       </c>
-      <c r="C87" s="11" t="inlineStr">
+      <c r="C87" s="10" t="inlineStr">
         <is>
           <t>Exceção</t>
         </is>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>3</v>
@@ -4662,10 +4662,10 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D13" s="8" t="n">
         <v>41</v>
